--- a/data/trans_orig/Q5407-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5407-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2007</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,62 +768,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4656</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4824</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27528</t>
+          <t>26958</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34490</t>
+          <t>34481</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>30130</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38116</t>
+          <t>38095</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61147</t>
+          <t>61547</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71903</t>
+          <t>71351</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,67 +1204,67 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7091</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2840</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>13541</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>2,9%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>13,84%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>7091</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2869</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>13636</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>13,93%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>7091</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14036</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>9053</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>15701</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57784</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65672</t>
+          <t>65664</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73336</t>
+          <t>74438</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88758</t>
+          <t>89443</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135359</t>
+          <t>135587</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152361</t>
+          <t>152406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,63%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19987</t>
+          <t>19029</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22600</t>
+          <t>22685</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41952</t>
+          <t>42248</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49869</t>
+          <t>49986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59867</t>
+          <t>60523</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75409</t>
+          <t>75033</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>106475</t>
+          <t>106529</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123366</t>
+          <t>122518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>11236</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>841</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18507</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22471</t>
+          <t>22587</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47426</t>
+          <t>47117</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54223</t>
+          <t>54281</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50488</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>64161</t>
+          <t>64898</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>100536</t>
+          <t>100408</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116134</t>
+          <t>116401</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,93%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10551</t>
+          <t>9550</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>16337</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22039</t>
+          <t>22151</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>17754</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25892</t>
+          <t>25938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23082</t>
+          <t>22992</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34837</t>
+          <t>34515</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44676</t>
+          <t>44105</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58817</t>
+          <t>58801</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,3%</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15228</t>
+          <t>15459</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23105</t>
+          <t>22833</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44425</t>
+          <t>44357</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>50142</t>
+          <t>50509</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63971</t>
+          <t>63354</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>89485</t>
+          <t>89894</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>106563</t>
+          <t>106482</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>888</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>9099</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>11478</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17610</t>
+          <t>17619</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>25455</t>
+          <t>24373</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>93251</t>
+          <t>93617</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>103408</t>
+          <t>103455</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>95630</t>
+          <t>95988</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>109951</t>
+          <t>109836</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>193516</t>
+          <t>194674</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>210842</t>
+          <t>211579</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>11276</t>
+          <t>11992</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29275</t>
+          <t>29307</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>19205</t>
+          <t>18616</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>10560</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>26862</t>
+          <t>27703</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>19800</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>41427</t>
+          <t>40712</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>87568</t>
+          <t>88318</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>102554</t>
+          <t>102349</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>110243</t>
+          <t>110969</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>131751</t>
+          <t>131579</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>203157</t>
+          <t>202743</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>229488</t>
+          <t>228922</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,35%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>17413</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>26369</t>
+          <t>27248</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>51829</t>
+          <t>52245</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>36213</t>
+          <t>36684</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>64561</t>
+          <t>64379</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>29684</t>
+          <t>30225</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>53112</t>
+          <t>53759</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>64752</t>
+          <t>64499</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>98609</t>
+          <t>99112</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>101932</t>
+          <t>99345</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>143944</t>
+          <t>142200</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>437973</t>
+          <t>437558</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>462787</t>
+          <t>462859</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>537075</t>
+          <t>537481</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>576837</t>
+          <t>578079</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>984044</t>
+          <t>985298</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1031457</t>
+          <t>1035390</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,8%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2012</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16742</t>
+          <t>17049</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19546</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12095</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27309</t>
+          <t>26612</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31885</t>
+          <t>31798</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41493</t>
+          <t>41500</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18236</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32132</t>
+          <t>32531</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53071</t>
+          <t>53401</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71358</t>
+          <t>72660</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>11753</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>9825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>25837</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13698</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33306</t>
+          <t>31979</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23276</t>
+          <t>22141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25283</t>
+          <t>25037</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18711</t>
+          <t>19038</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>41494</t>
+          <t>41885</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52020</t>
+          <t>51947</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69199</t>
+          <t>69331</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59349</t>
+          <t>58123</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78413</t>
+          <t>78385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117546</t>
+          <t>117645</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143193</t>
+          <t>144105</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>18005</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22721</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13540</t>
+          <t>12689</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22912</t>
+          <t>22679</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36916</t>
+          <t>36647</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49663</t>
+          <t>49640</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54313</t>
+          <t>54138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69536</t>
+          <t>69432</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97340</t>
+          <t>96513</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116125</t>
+          <t>116650</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12146</t>
+          <t>11633</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16339</t>
+          <t>16726</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23053</t>
+          <t>22995</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22232</t>
+          <t>23339</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27989</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47047</t>
+          <t>47165</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59006</t>
+          <t>58824</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53217</t>
+          <t>51273</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69766</t>
+          <t>69291</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>105479</t>
+          <t>106210</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>126718</t>
+          <t>126002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15106</t>
+          <t>15130</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17328</t>
+          <t>17341</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12515</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>16792</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21111</t>
+          <t>20282</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29420</t>
+          <t>29457</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>28083</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41238</t>
+          <t>40625</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52882</t>
+          <t>52745</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68946</t>
+          <t>67996</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9576</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13873</t>
+          <t>13338</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6258</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20310</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>11643</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18559</t>
+          <t>19067</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10517</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24860</t>
+          <t>26107</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35817</t>
+          <t>34904</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46483</t>
+          <t>47454</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42966</t>
+          <t>42799</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57634</t>
+          <t>58420</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>83733</t>
+          <t>83892</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>102127</t>
+          <t>101914</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19799</t>
+          <t>20263</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19384</t>
+          <t>18656</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12841</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>33138</t>
+          <t>33725</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12397</t>
+          <t>12561</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29672</t>
+          <t>30557</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>21096</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>42944</t>
+          <t>41738</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>80297</t>
+          <t>81570</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>99669</t>
+          <t>99821</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>100065</t>
+          <t>100135</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>120635</t>
+          <t>120220</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>187391</t>
+          <t>188198</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>214763</t>
+          <t>215405</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,73%</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25123</t>
+          <t>24867</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>10861</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>28308</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>14470</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>24561</t>
+          <t>24260</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>14020</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>32458</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>103237</t>
+          <t>103112</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>117376</t>
+          <t>117379</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>121482</t>
+          <t>123072</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>142817</t>
+          <t>143098</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>231908</t>
+          <t>230873</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>256374</t>
+          <t>256438</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>23538</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>49044</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>71919</t>
+          <t>73389</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>108427</t>
+          <t>108386</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>102669</t>
+          <t>101386</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>147630</t>
+          <t>147138</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>40749</t>
+          <t>40904</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>73353</t>
+          <t>72759</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>86014</t>
+          <t>84986</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>124891</t>
+          <t>122128</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>136634</t>
+          <t>134633</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>185209</t>
+          <t>183096</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>449764</t>
+          <t>450990</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>488342</t>
+          <t>487987</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>524561</t>
+          <t>524506</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>574031</t>
+          <t>573159</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>991325</t>
+          <t>989582</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1050990</t>
+          <t>1050794</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2016</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5998</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>10963</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9356</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23726</t>
+          <t>24087</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13207</t>
+          <t>14560</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30266</t>
+          <t>30931</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25601</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>34303</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23573</t>
+          <t>23313</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37874</t>
+          <t>38031</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52901</t>
+          <t>52504</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70441</t>
+          <t>70199</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24596</t>
+          <t>25253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29617</t>
+          <t>29932</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>855</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22882</t>
+          <t>23448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9463</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27438</t>
+          <t>26870</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75563</t>
+          <t>75230</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84668</t>
+          <t>84687</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75191</t>
+          <t>74528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95708</t>
+          <t>94694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154457</t>
+          <t>153686</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>178613</t>
+          <t>177541</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,66%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>824</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>10257</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17321</t>
+          <t>15587</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13491</t>
+          <t>12971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50988</t>
+          <t>51424</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60546</t>
+          <t>60531</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62841</t>
+          <t>63701</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76699</t>
+          <t>77315</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119078</t>
+          <t>120541</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135217</t>
+          <t>135295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2278</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10571</t>
+          <t>10796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28336</t>
+          <t>28304</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34389</t>
+          <t>35439</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49189</t>
+          <t>49388</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60319</t>
+          <t>60200</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63238</t>
+          <t>63270</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>80778</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>117550</t>
+          <t>117338</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>137756</t>
+          <t>138412</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>979</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9572</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22535</t>
+          <t>23384</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10562</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27245</t>
+          <t>26503</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33485</t>
+          <t>33424</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40471</t>
+          <t>40504</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23525</t>
+          <t>23506</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>38066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59278</t>
+          <t>59302</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77222</t>
+          <t>77025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,17%</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>17556</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20922</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>15538</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17782</t>
+          <t>18820</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29019</t>
+          <t>29568</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29957</t>
+          <t>30303</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41164</t>
+          <t>41223</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>38484</t>
+          <t>38602</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55033</t>
+          <t>54454</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>74029</t>
+          <t>74454</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>94031</t>
+          <t>94194</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,32%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14415</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19125</t>
+          <t>19067</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28909</t>
+          <t>27614</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17147</t>
+          <t>18914</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25902</t>
+          <t>25530</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>48193</t>
+          <t>47693</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>35137</t>
+          <t>34592</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60152</t>
+          <t>59665</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>86051</t>
+          <t>85759</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>101160</t>
+          <t>101652</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>88361</t>
+          <t>88917</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>112672</t>
+          <t>112614</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>180322</t>
+          <t>178572</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>209684</t>
+          <t>208967</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,43%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>15042</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>18674</t>
+          <t>17656</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10376</t>
+          <t>9606</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>27634</t>
+          <t>27496</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>18726</t>
+          <t>18155</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>12957</t>
+          <t>12737</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>32515</t>
+          <t>32987</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>21881</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>44671</t>
+          <t>45740</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>105113</t>
+          <t>106133</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>121297</t>
+          <t>121894</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>133199</t>
+          <t>132243</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>155276</t>
+          <t>156042</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>245486</t>
+          <t>245964</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>273301</t>
+          <t>274570</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>23045</t>
+          <t>21868</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>44136</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>39614</t>
+          <t>40666</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>73698</t>
+          <t>71849</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>70277</t>
+          <t>68665</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>107258</t>
+          <t>109238</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>39814</t>
+          <t>38959</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>65152</t>
+          <t>65481</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>111117</t>
+          <t>114610</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>155950</t>
+          <t>160447</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>159542</t>
+          <t>160084</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>215193</t>
+          <t>212281</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>492462</t>
+          <t>490224</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>523067</t>
+          <t>524113</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>562737</t>
+          <t>559428</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>615236</t>
+          <t>612118</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1061556</t>
+          <t>1063801</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1123318</t>
+          <t>1126045</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2023</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2023 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>403</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>404</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9613</t>
+          <t>10539</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>10934</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46288</t>
+          <t>45362</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53833</t>
+          <t>53486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50850</t>
+          <t>50579</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59085</t>
+          <t>59325</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>100504</t>
+          <t>100479</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>111127</t>
+          <t>111360</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>10480</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22686</t>
+          <t>23917</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15278</t>
+          <t>15311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29208</t>
+          <t>29674</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12320</t>
+          <t>13039</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32422</t>
+          <t>32680</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24703</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>41238</t>
+          <t>42142</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62272</t>
+          <t>61438</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73813</t>
+          <t>73673</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78478</t>
+          <t>78155</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94667</t>
+          <t>94266</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145335</t>
+          <t>144039</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>165746</t>
+          <t>166335</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,55%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18258</t>
+          <t>18811</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10968</t>
+          <t>11588</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>21543</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22472</t>
+          <t>22713</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36357</t>
+          <t>37198</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>8934</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12525</t>
+          <t>12523</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23118</t>
+          <t>23547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16392</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29766</t>
+          <t>29249</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50074</t>
+          <t>50207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61650</t>
+          <t>61167</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45244</t>
+          <t>45090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58957</t>
+          <t>58561</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99163</t>
+          <t>99535</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116654</t>
+          <t>115556</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>72,71%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17254</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>14661</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12030</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22527</t>
+          <t>22668</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60216</t>
+          <t>60076</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69026</t>
+          <t>69119</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79443</t>
+          <t>79093</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88734</t>
+          <t>88736</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>142639</t>
+          <t>142633</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>155473</t>
+          <t>155698</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,32%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10922</t>
+          <t>10912</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6935</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15315</t>
+          <t>14788</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>23460</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29993</t>
+          <t>30439</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38705</t>
+          <t>37993</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47099</t>
+          <t>46769</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64800</t>
+          <t>64584</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75512</t>
+          <t>74977</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>79,71%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>12404</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21078</t>
+          <t>20581</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31484</t>
+          <t>31096</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>11460</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19968</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>28651</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39122</t>
+          <t>39073</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>48120</t>
+          <t>47809</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28057</t>
+          <t>28922</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38541</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>70256</t>
+          <t>70297</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>83376</t>
+          <t>83716</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,7%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52587</t>
+          <t>52230</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>44379</t>
+          <t>45325</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>13185</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>63855</t>
+          <t>64374</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>59675</t>
+          <t>60833</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>104440</t>
+          <t>104499</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>116453</t>
+          <t>115651</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>226924</t>
+          <t>227553</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>327716</t>
+          <t>328126</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>359375</t>
+          <t>358888</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>444038</t>
+          <t>444477</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16339</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>18643</t>
+          <t>18543</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>13144</t>
+          <t>12978</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>25786</t>
+          <t>26064</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>38462</t>
+          <t>38851</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>55283</t>
+          <t>56540</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>55080</t>
+          <t>56509</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>77587</t>
+          <t>76997</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>118723</t>
+          <t>119275</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>132356</t>
+          <t>132388</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>120620</t>
+          <t>119359</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>138359</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>242928</t>
+          <t>243899</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>266949</t>
+          <t>265336</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>31286</t>
+          <t>31584</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>50893</t>
+          <t>50537</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>51468</t>
+          <t>54579</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>124203</t>
+          <t>124378</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>89073</t>
+          <t>87297</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>160899</t>
+          <t>160311</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>49934</t>
+          <t>50060</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>73775</t>
+          <t>74595</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>85721</t>
+          <t>89660</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>200148</t>
+          <t>198117</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>137222</t>
+          <t>139888</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>252087</t>
+          <t>252228</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>532246</t>
+          <t>532550</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>561651</t>
+          <t>562169</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>710044</t>
+          <t>712522</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>890520</t>
+          <t>885516</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1272695</t>
+          <t>1272442</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1454037</t>
+          <t>1458269</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
